--- a/output/yearly_surface_area_iteration_60_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_60_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497615657475</v>
+        <v>10.8449764993313</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907132989487</v>
+        <v>37.78907252422223</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.497206306705391</v>
+        <v>5.361324212891832</v>
       </c>
       <c r="C2" t="n">
-        <v>11.79471691882118</v>
+        <v>4.061490252469055</v>
       </c>
       <c r="D2" t="n">
-        <v>20.0688865702133</v>
+        <v>34.9011308859741</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.42602175038088</v>
+        <v>16.38046044535803</v>
       </c>
       <c r="C3" t="n">
-        <v>36.72227287735194</v>
+        <v>18.67775007329557</v>
       </c>
       <c r="D3" t="n">
-        <v>69.8268054645544</v>
+        <v>88.05295159389642</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.97810811753286</v>
+        <v>34.15303913533804</v>
       </c>
       <c r="C4" t="n">
-        <v>88.73919323916495</v>
+        <v>57.35566437750716</v>
       </c>
       <c r="D4" t="n">
-        <v>102.3697783649277</v>
+        <v>109.5679525324653</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.28878236043136</v>
+        <v>43.61414176116455</v>
       </c>
       <c r="C5" t="n">
-        <v>138.966387536136</v>
+        <v>101.3899941560894</v>
       </c>
       <c r="D5" t="n">
-        <v>81.97593330460867</v>
+        <v>78.34346679889548</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.27932473628739</v>
+        <v>39.08435785376978</v>
       </c>
       <c r="C6" t="n">
-        <v>142.0883452356409</v>
+        <v>136.6543716926348</v>
       </c>
       <c r="D6" t="n">
-        <v>55.2252718592916</v>
+        <v>50.2340665309008</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.30829414132927</v>
+        <v>26.82920126165683</v>
       </c>
       <c r="C7" t="n">
-        <v>106.897598776914</v>
+        <v>131.750541909922</v>
       </c>
       <c r="D7" t="n">
-        <v>40.96244121199391</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>13.68556299720053</v>
       </c>
       <c r="C8" t="n">
-        <v>65.17332134642452</v>
+        <v>90.95892479846698</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>49.69999577979051</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.665168575595163</v>
+        <v>7.653346275316912</v>
       </c>
       <c r="C21" t="n">
-        <v>93.89831505104074</v>
+        <v>92.79682358821756</v>
       </c>
       <c r="D21" t="n">
-        <v>7.665168575595163</v>
+        <v>7.653346275316912</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.330710107610932</v>
+        <v>5.723589115758905</v>
       </c>
       <c r="C2" t="n">
-        <v>13.44012607113883</v>
+        <v>11.72501283181966</v>
       </c>
       <c r="D2" t="n">
-        <v>34.26201313050944</v>
+        <v>37.16994983048848</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.30115986549229</v>
+        <v>16.94987411382118</v>
       </c>
       <c r="C3" t="n">
-        <v>40.97324043674063</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D3" t="n">
-        <v>69.14939954862409</v>
+        <v>93.3396629812655</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.12751369502762</v>
+        <v>32.26415655236718</v>
       </c>
       <c r="C4" t="n">
-        <v>89.13483756397642</v>
+        <v>51.54862670688727</v>
       </c>
       <c r="D4" t="n">
-        <v>110.4358175030195</v>
+        <v>123.5176056621082</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.19752088166541</v>
+        <v>46.80482179996669</v>
       </c>
       <c r="C5" t="n">
-        <v>150.354660905399</v>
+        <v>102.3226544751238</v>
       </c>
       <c r="D5" t="n">
-        <v>97.11939164261574</v>
+        <v>96.28490609400595</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.97368240509714</v>
+        <v>47.85921883432777</v>
       </c>
       <c r="C6" t="n">
-        <v>176.4230076962646</v>
+        <v>148.4078552078776</v>
       </c>
       <c r="D6" t="n">
-        <v>65.32843748369551</v>
+        <v>60.33723215530473</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.33309987584271</v>
+        <v>35.99185258539232</v>
       </c>
       <c r="C7" t="n">
-        <v>151.8724428561646</v>
+        <v>161.2147540097772</v>
       </c>
       <c r="D7" t="n">
-        <v>46.59178254814513</v>
+        <v>44.31609136970101</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.19593293468863</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C8" t="n">
-        <v>98.96998606512095</v>
+        <v>129.9293999185441</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.53906160508951</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>56.68905768632355</v>
+        <v>77.76718089650257</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>36.72718161587318</v>
+        <v>44.27191272300992</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.62994753542373</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
         <v>35.36549755008285</v>
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.837993071630868</v>
+        <v>7.827023424925805</v>
       </c>
       <c r="C21" t="n">
-        <v>101.8939099312013</v>
+        <v>100.7729265959197</v>
       </c>
       <c r="D21" t="n">
-        <v>8.817742205584727</v>
+        <v>8.80540135304153</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.85241904919349</v>
+        <v>7.200137662946108</v>
       </c>
       <c r="C2" t="n">
-        <v>16.97049081561036</v>
+        <v>16.42758433516188</v>
       </c>
       <c r="D2" t="n">
-        <v>38.40498844243097</v>
+        <v>30.87596529856219</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.07812321017902</v>
+        <v>17.56837516749667</v>
       </c>
       <c r="C3" t="n">
-        <v>45.53345852296707</v>
+        <v>29.8402214705818</v>
       </c>
       <c r="D3" t="n">
-        <v>76.9788374899924</v>
+        <v>98.46438599743385</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.28066633689012</v>
+        <v>31.47286790274425</v>
       </c>
       <c r="C4" t="n">
-        <v>93.60178961829939</v>
+        <v>47.00509833163304</v>
       </c>
       <c r="D4" t="n">
-        <v>117.0596692635727</v>
+        <v>135.7315288506427</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.35107443415542</v>
+        <v>47.56567627075797</v>
       </c>
       <c r="C5" t="n">
-        <v>154.2571080297801</v>
+        <v>97.88024611340703</v>
       </c>
       <c r="D5" t="n">
-        <v>108.7040145527281</v>
+        <v>113.6863841517807</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.3736956890821</v>
+        <v>53.73596059194917</v>
       </c>
       <c r="C6" t="n">
-        <v>202.5060807026939</v>
+        <v>154.8883718036108</v>
       </c>
       <c r="D6" t="n">
-        <v>77.08192099893833</v>
+        <v>72.05046401467342</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.47767883027424</v>
+        <v>44.31609136970101</v>
       </c>
       <c r="C7" t="n">
-        <v>192.5953376283223</v>
+        <v>182.8937068149553</v>
       </c>
       <c r="D7" t="n">
-        <v>52.10135066437822</v>
+        <v>50.06520592577034</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.20561154301086</v>
+        <v>27.78836876870596</v>
       </c>
       <c r="C8" t="n">
-        <v>139.8597779470006</v>
+        <v>164.7274472955723</v>
       </c>
       <c r="D8" t="n">
-        <v>40.97324043674063</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.64374875654542</v>
+        <v>14.19999879422586</v>
       </c>
       <c r="C9" t="n">
-        <v>83.20311793491715</v>
+        <v>113.0453029009074</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>49.39663573917827</v>
+        <v>63.34727061652544</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>35.89465956267188</v>
+        <v>39.98167525545134</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
         <v>35.58246379272139</v>
@@ -1559,7 +1559,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>33.56104526967722</v>
@@ -1573,7 +1573,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.993061223155037</v>
+        <v>7.985431263664155</v>
       </c>
       <c r="C21" t="n">
-        <v>108.9054591654874</v>
+        <v>107.8033220594661</v>
       </c>
       <c r="D21" t="n">
-        <v>9.991326528943796</v>
+        <v>9.981789079580194</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.094509821514952</v>
+        <v>6.546293691917731</v>
       </c>
       <c r="C2" t="n">
-        <v>11.94688781297944</v>
+        <v>11.30187957128928</v>
       </c>
       <c r="D2" t="n">
-        <v>31.46206867799753</v>
+        <v>25.64521353033518</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.16081100151401</v>
+        <v>21.38737373701677</v>
       </c>
       <c r="C3" t="n">
-        <v>67.406797373586</v>
+        <v>45.47946239923349</v>
       </c>
       <c r="D3" t="n">
-        <v>84.03269474500574</v>
+        <v>105.8324025178061</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.22815068247953</v>
+        <v>22.84526907782328</v>
       </c>
       <c r="C4" t="n">
-        <v>126.4147431373405</v>
+        <v>74.12587866145118</v>
       </c>
       <c r="D4" t="n">
-        <v>115.4770919643268</v>
+        <v>129.4650332544354</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.06602344255857</v>
+        <v>30.26237298340794</v>
       </c>
       <c r="C5" t="n">
-        <v>121.0004045484194</v>
+        <v>92.55426481786806</v>
       </c>
       <c r="D5" t="n">
-        <v>75.2755052231242</v>
+        <v>73.60653412590462</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.96860943565989</v>
+        <v>27.49188096202344</v>
       </c>
       <c r="C6" t="n">
-        <v>126.8329676593497</v>
+        <v>120.4329543753648</v>
       </c>
       <c r="D6" t="n">
-        <v>34.29441080474959</v>
+        <v>32.96610616090365</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>18.38518925743002</v>
       </c>
       <c r="C7" t="n">
-        <v>98.333813552769</v>
+        <v>115.8207036608132</v>
       </c>
       <c r="D7" t="n">
-        <v>28.80545939030566</v>
+        <v>28.086820070797</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>61.33468782281948</v>
+        <v>83.28165775125692</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>48.36874589283183</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.04362317181014</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>28.43141351498762</v>
@@ -1856,7 +1856,7 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
         <v>27.33774657245668</v>
@@ -1870,7 +1870,7 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.912665512051039</v>
+        <v>3.947607518776425</v>
       </c>
       <c r="C2" t="n">
-        <v>5.341689258806895</v>
+        <v>5.619523859108742</v>
       </c>
       <c r="D2" t="n">
-        <v>21.72214970416493</v>
+        <v>18.53441490847553</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.41883072128167</v>
+        <v>22.41820882647592</v>
       </c>
       <c r="C3" t="n">
-        <v>58.18818643070845</v>
+        <v>45.7396255408589</v>
       </c>
       <c r="D3" t="n">
-        <v>88.70581381722056</v>
+        <v>103.795276031494</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.69808903764427</v>
+        <v>30.42632485001715</v>
       </c>
       <c r="C4" t="n">
-        <v>150.6766741523919</v>
+        <v>94.62280723071608</v>
       </c>
       <c r="D4" t="n">
-        <v>129.0055753288479</v>
+        <v>147.741248516694</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.57577148524092</v>
+        <v>33.30579086657305</v>
       </c>
       <c r="C5" t="n">
-        <v>172.3458094805276</v>
+        <v>115.2080930933632</v>
       </c>
       <c r="D5" t="n">
-        <v>91.32708018755955</v>
+        <v>95.35224577497146</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.87931145230244</v>
+        <v>32.72459622565894</v>
       </c>
       <c r="C6" t="n">
-        <v>156.7399479738203</v>
+        <v>138.3046895834737</v>
       </c>
       <c r="D6" t="n">
-        <v>42.58625191481815</v>
+        <v>41.09694064747573</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>17.12757044828985</v>
       </c>
       <c r="C7" t="n">
-        <v>129.9539436111503</v>
+        <v>140.9730798436165</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>81.52923809917637</v>
+        <v>108.0658785449676</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60155896745857</v>
+        <v>52.69530802544753</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>29.60951076008381</v>
@@ -2153,7 +2153,7 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.508586368528853</v>
+        <v>3.987859174650544</v>
       </c>
       <c r="C2" t="n">
-        <v>9.605419538350793</v>
+        <v>11.3254415161912</v>
       </c>
       <c r="D2" t="n">
-        <v>17.54088623177776</v>
+        <v>17.57132041060941</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.78498155723672</v>
+        <v>17.89726064841935</v>
       </c>
       <c r="C3" t="n">
-        <v>38.95574890451343</v>
+        <v>33.41869185256143</v>
       </c>
       <c r="D3" t="n">
-        <v>86.30053194181586</v>
+        <v>95.30315838975912</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.36848385092459</v>
+        <v>36.42480332296516</v>
       </c>
       <c r="C4" t="n">
-        <v>147.8305875577805</v>
+        <v>104.3097118285194</v>
       </c>
       <c r="D4" t="n">
-        <v>139.4454804158084</v>
+        <v>163.1713771843411</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.2761995667254</v>
+        <v>38.92629647338604</v>
       </c>
       <c r="C5" t="n">
-        <v>223.3721464087556</v>
+        <v>143.5560580534899</v>
       </c>
       <c r="D5" t="n">
-        <v>112.6064616771092</v>
+        <v>121.4421910153305</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.59504658642736</v>
+        <v>38.19882142453915</v>
       </c>
       <c r="C6" t="n">
-        <v>208.4633257720635</v>
+        <v>160.684610249484</v>
       </c>
       <c r="D6" t="n">
-        <v>57.43911293236815</v>
+        <v>57.11709968537519</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.21226279276233</v>
+        <v>25.75124228239384</v>
       </c>
       <c r="C7" t="n">
-        <v>173.6112822713017</v>
+        <v>169.598879404045</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>12.01659189998096</v>
       </c>
       <c r="C8" t="n">
-        <v>120.3328161095315</v>
+        <v>143.6984114706056</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.2069942013426</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>65.45311944213483</v>
+        <v>86.08749268999428</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>38.43542262126263</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.308489763311751</v>
+        <v>2.390555659840983</v>
       </c>
       <c r="C2" t="n">
-        <v>4.708461989567702</v>
+        <v>5.372123437638546</v>
       </c>
       <c r="D2" t="n">
-        <v>12.38376554136927</v>
+        <v>12.30522572502952</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.46729621168826</v>
+        <v>17.7303635386974</v>
       </c>
       <c r="C3" t="n">
-        <v>40.78670837293374</v>
+        <v>40.06512381031234</v>
       </c>
       <c r="D3" t="n">
-        <v>84.63646958311753</v>
+        <v>92.39227644666732</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.95480821453819</v>
+        <v>40.11322944782042</v>
       </c>
       <c r="C4" t="n">
-        <v>145.0866027244106</v>
+        <v>106.6325268967673</v>
       </c>
       <c r="D4" t="n">
-        <v>149.5407920585784</v>
+        <v>173.9558757154923</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.30703465618456</v>
+        <v>40.66889864842413</v>
       </c>
       <c r="C5" t="n">
-        <v>269.8088128196297</v>
+        <v>178.4817326320702</v>
       </c>
       <c r="D5" t="n">
-        <v>115.1835494007571</v>
+        <v>128.1917064820273</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.22899356146354</v>
+        <v>31.15478164656829</v>
       </c>
       <c r="C6" t="n">
-        <v>238.4910610541564</v>
+        <v>193.8922263456323</v>
       </c>
       <c r="D6" t="n">
-        <v>55.58753676215866</v>
+        <v>55.4667817945363</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.905032514595317</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>170.676838383308</v>
+        <v>182.0552942755285</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>82.44717220264712</v>
+        <v>105.6458704539993</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.19655482949439</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.450843180427539</v>
+        <v>3.159264112266236</v>
       </c>
       <c r="C2" t="n">
-        <v>4.243113577754714</v>
+        <v>9.030115383662162</v>
       </c>
       <c r="D2" t="n">
-        <v>13.99186828092554</v>
+        <v>17.8835161805599</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.21985473248905</v>
+        <v>13.1897804065559</v>
       </c>
       <c r="C3" t="n">
-        <v>29.99239236474006</v>
+        <v>30.52744486355457</v>
       </c>
       <c r="D3" t="n">
-        <v>76.98865496703488</v>
+        <v>82.86932371547327</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.49535028895069</v>
+        <v>37.13951565165684</v>
       </c>
       <c r="C4" t="n">
-        <v>124.8194031179395</v>
+        <v>103.2759314959475</v>
       </c>
       <c r="D4" t="n">
-        <v>155.1436262067149</v>
+        <v>178.8439975349372</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.85453107998479</v>
+        <v>48.91557936409734</v>
       </c>
       <c r="C5" t="n">
-        <v>270.6678420608457</v>
+        <v>188.2010349041136</v>
       </c>
       <c r="D5" t="n">
-        <v>134.8430471782994</v>
+        <v>153.9871274111122</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.08435785376978</v>
+        <v>40.37241084174159</v>
       </c>
       <c r="C6" t="n">
-        <v>319.034624458269</v>
+        <v>234.8281603696116</v>
       </c>
       <c r="D6" t="n">
-        <v>71.48694083243576</v>
+        <v>76.07562960208534</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="C7" t="n">
-        <v>242.4808837242155</v>
+        <v>227.2097981846563</v>
       </c>
       <c r="D7" t="n">
-        <v>40.54323494228053</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>135.7707987588126</v>
+        <v>159.8874311136355</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>32.7952820603647</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>53.69374544066654</v>
+        <v>68.67030666895162</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.473022466997715</v>
+        <v>2.061670178918302</v>
       </c>
       <c r="C2" t="n">
-        <v>2.832342126752048</v>
+        <v>4.693735774004001</v>
       </c>
       <c r="D2" t="n">
-        <v>9.982410656781568</v>
+        <v>13.0955326269482</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.12382338392211</v>
+        <v>12.27184630308513</v>
       </c>
       <c r="C3" t="n">
-        <v>24.51914891356409</v>
+        <v>32.81982575297087</v>
       </c>
       <c r="D3" t="n">
-        <v>72.13391256953439</v>
+        <v>79.2270397327176</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.93455136564751</v>
+        <v>33.46385224695678</v>
       </c>
       <c r="C4" t="n">
-        <v>108.2789177967892</v>
+        <v>94.68662083149212</v>
       </c>
       <c r="D4" t="n">
-        <v>159.0234931338983</v>
+        <v>179.686337065181</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.52412407201012</v>
+        <v>52.54804586981054</v>
       </c>
       <c r="C5" t="n">
-        <v>262.8138604268712</v>
+        <v>193.2815792735908</v>
       </c>
       <c r="D5" t="n">
-        <v>147.7284857965388</v>
+        <v>172.2967220953152</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.80009298789471</v>
+        <v>47.13468902859362</v>
       </c>
       <c r="C6" t="n">
-        <v>367.4171148189604</v>
+        <v>266.7477234777882</v>
       </c>
       <c r="D6" t="n">
-        <v>83.52218593879741</v>
+        <v>90.2039608139012</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.49255961009142</v>
+        <v>15.21119892960008</v>
       </c>
       <c r="C7" t="n">
-        <v>309.0747939986851</v>
+        <v>271.4061163344392</v>
       </c>
       <c r="D7" t="n">
-        <v>45.8132566186774</v>
+        <v>44.67541102945535</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>176.1598993115264</v>
+        <v>199.9427374469054</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>57.68749510154256</v>
+        <v>77.10155595302322</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.986476516318797</v>
+        <v>2.719441140763665</v>
       </c>
       <c r="C2" t="n">
-        <v>11.70145088691773</v>
+        <v>11.96652276706437</v>
       </c>
       <c r="D2" t="n">
-        <v>16.25381499151019</v>
+        <v>22.19829734072463</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.99204820737479</v>
+        <v>9.76348091873453</v>
       </c>
       <c r="C3" t="n">
-        <v>18.53048791765854</v>
+        <v>26.03104037810418</v>
       </c>
       <c r="D3" t="n">
-        <v>65.14386891529711</v>
+        <v>73.26292242941823</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.52315801983909</v>
+        <v>28.89479843139213</v>
       </c>
       <c r="C4" t="n">
-        <v>88.49670155621598</v>
+        <v>88.85405772056183</v>
       </c>
       <c r="D4" t="n">
-        <v>158.0152382416369</v>
+        <v>176.0234363806361</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.87402716534948</v>
+        <v>51.51721078035138</v>
       </c>
       <c r="C5" t="n">
-        <v>236.8957210347554</v>
+        <v>184.8385490170683</v>
       </c>
       <c r="D5" t="n">
-        <v>162.9455752123644</v>
+        <v>190.3363361608504</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.58124536530568</v>
+        <v>55.6680400739069</v>
       </c>
       <c r="C6" t="n">
-        <v>387.1404261972788</v>
+        <v>283.3314056979253</v>
       </c>
       <c r="D6" t="n">
-        <v>100.7498946529204</v>
+        <v>113.0266496945268</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.29022177202533</v>
+        <v>28.14670668075605</v>
       </c>
       <c r="C7" t="n">
-        <v>390.4008103230823</v>
+        <v>319.4351775216017</v>
       </c>
       <c r="D7" t="n">
-        <v>53.29908286355933</v>
+        <v>54.73636150257666</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.260024272905162</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>260.1091455016712</v>
+        <v>259.1912113982004</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>109.495303202351</v>
+        <v>136.8968633755837</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>42.27896488338889</v>
+        <v>51.24723016168351</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.486987919035423</v>
+        <v>5.546874528994478</v>
       </c>
       <c r="C2" t="n">
-        <v>6.097634991076939</v>
+        <v>11.60818485501428</v>
       </c>
       <c r="D2" t="n">
-        <v>19.88333625411065</v>
+        <v>9.469938355164732</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.205987091442583</v>
+        <v>1.988039101099791</v>
       </c>
       <c r="C2" t="n">
-        <v>7.021459580773187</v>
+        <v>6.988080158828796</v>
       </c>
       <c r="D2" t="n">
-        <v>12.22374066557704</v>
+        <v>16.51495988083985</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.81104677689488</v>
+        <v>12.9885221271853</v>
       </c>
       <c r="C3" t="n">
-        <v>28.89774367450487</v>
+        <v>35.99087083768807</v>
       </c>
       <c r="D3" t="n">
-        <v>71.10307748007524</v>
+        <v>81.74522259411067</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.1545039091278</v>
+        <v>39.51338160052563</v>
       </c>
       <c r="C4" t="n">
-        <v>129.0566262094687</v>
+        <v>121.6542485194477</v>
       </c>
       <c r="D4" t="n">
-        <v>160.6954094742306</v>
+        <v>179.2141164194383</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.72870314292517</v>
+        <v>31.83316931020283</v>
       </c>
       <c r="C5" t="n">
-        <v>337.5494044126596</v>
+        <v>255.9416264971435</v>
       </c>
       <c r="D5" t="n">
-        <v>146.452213781018</v>
+        <v>171.4867802393116</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.30192062901829</v>
+        <v>17.46921864936775</v>
       </c>
       <c r="C6" t="n">
-        <v>321.6107304342127</v>
+        <v>260.3477101938032</v>
       </c>
       <c r="D6" t="n">
-        <v>79.25551041614078</v>
+        <v>85.61527204425161</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.790928796724434</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>182.8937068149553</v>
+        <v>182.2349541054057</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9794497181356</v>
+        <v>32.75797564760332</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>80.69475255056658</v>
+        <v>100.8893028269235</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>24.11663235482289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>32.28280975874785</v>
+        <v>39.04999668412111</v>
       </c>
       <c r="D9" t="n">
-        <v>19.74687332322034</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.64124548178919</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74879576089983</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
         <v>15.99267010218054</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.0179745583127</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.837872760079034</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C2" t="n">
-        <v>4.429645641561608</v>
+        <v>5.673519982842318</v>
       </c>
       <c r="D2" t="n">
-        <v>22.92282714645878</v>
+        <v>22.81188965587889</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.65825398793087</v>
+        <v>11.78588118948296</v>
       </c>
       <c r="C3" t="n">
-        <v>15.36435157146258</v>
+        <v>29.25117284803371</v>
       </c>
       <c r="D3" t="n">
-        <v>19.8362123643068</v>
+        <v>11.08884031946772</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39660227380446</v>
+        <v>13.39743156710496</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13515308050569</v>
+        <v>70.13949467484359</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576070855741701</v>
+        <v>1.576168419659406</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.217588137444298</v>
+        <v>5.05698242457532</v>
       </c>
       <c r="C2" t="n">
-        <v>9.213702204356315</v>
+        <v>6.8791061636574</v>
       </c>
       <c r="D2" t="n">
-        <v>30.85043985825177</v>
+        <v>26.17437554292421</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.81519475189012</v>
+        <v>17.19531103988288</v>
       </c>
       <c r="C3" t="n">
-        <v>16.55717503212245</v>
+        <v>24.7940382707532</v>
       </c>
       <c r="D3" t="n">
-        <v>34.29735604786232</v>
+        <v>27.56747553525044</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.6050596854523</v>
+        <v>13.74544960715959</v>
       </c>
       <c r="C4" t="n">
-        <v>23.96838845148163</v>
+        <v>45.11621574866217</v>
       </c>
       <c r="D4" t="n">
-        <v>25.46162670964103</v>
+        <v>20.87981017392116</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43731967675481</v>
+        <v>15.43712017374265</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12399398610579</v>
+        <v>86.12288096930109</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249962037211539</v>
+        <v>3.2499200365774</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.437499623195583</v>
+        <v>4.568072067860409</v>
       </c>
       <c r="C2" t="n">
-        <v>7.715555207675683</v>
+        <v>7.67628529950581</v>
       </c>
       <c r="D2" t="n">
-        <v>22.66855449105885</v>
+        <v>33.26946620151591</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.43936530761284</v>
+        <v>17.5291052593268</v>
       </c>
       <c r="C3" t="n">
-        <v>28.04853191033137</v>
+        <v>25.95250056176443</v>
       </c>
       <c r="D3" t="n">
-        <v>51.0165194511855</v>
+        <v>42.1071590351457</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.55922064298896</v>
+        <v>24.47889725768997</v>
       </c>
       <c r="C4" t="n">
-        <v>33.85949657176824</v>
+        <v>54.94351026817274</v>
       </c>
       <c r="D4" t="n">
-        <v>36.90978668886309</v>
+        <v>29.99239236474006</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.00186568441726</v>
+        <v>12.12458414744811</v>
       </c>
       <c r="C5" t="n">
-        <v>27.58711048933538</v>
+        <v>48.98921044191585</v>
       </c>
       <c r="D5" t="n">
-        <v>31.78408192499049</v>
+        <v>30.16419821298325</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72654207395645</v>
+        <v>16.72422386260005</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0319066511343</v>
+        <v>102.0177655618603</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181635518489112</v>
+        <v>4.181055965650012</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.220934291184538</v>
+        <v>6.053456344385832</v>
       </c>
       <c r="C2" t="n">
-        <v>11.33722248864217</v>
+        <v>5.430046552189108</v>
       </c>
       <c r="D2" t="n">
-        <v>18.86133689398972</v>
+        <v>33.31069960509427</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.7275982220339</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C3" t="n">
-        <v>29.12845438500286</v>
+        <v>28.09761929554371</v>
       </c>
       <c r="D3" t="n">
-        <v>56.8971881996239</v>
+        <v>58.02619805950773</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.18834099496192</v>
+        <v>29.53293443915255</v>
       </c>
       <c r="C4" t="n">
-        <v>54.15222161854981</v>
+        <v>60.40595449460199</v>
       </c>
       <c r="D4" t="n">
-        <v>53.24606848753</v>
+        <v>43.57192660988194</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.89359569950963</v>
+        <v>24.02827506144069</v>
       </c>
       <c r="C5" t="n">
-        <v>46.4612101034803</v>
+        <v>76.33088400518952</v>
       </c>
       <c r="D5" t="n">
-        <v>37.28186906877263</v>
+        <v>33.69848994827177</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.98870205363455</v>
+        <v>11.10945702125691</v>
       </c>
       <c r="C6" t="n">
-        <v>28.45792070300229</v>
+        <v>46.08814597586652</v>
       </c>
       <c r="D6" t="n">
-        <v>38.7220929509027</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,7 +5546,7 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
         <v>42.15624642035802</v>
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5647,7 +5647,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0476827122767</v>
+        <v>18.03854078209885</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7396443610432</v>
+        <v>117.6800041498829</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015894237425565</v>
+        <v>6.012846927366281</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.629742246778711</v>
+        <v>6.183047041346412</v>
       </c>
       <c r="C2" t="n">
-        <v>10.60091171045706</v>
+        <v>6.387250563829748</v>
       </c>
       <c r="D2" t="n">
-        <v>26.65346842259665</v>
+        <v>24.48282424850696</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.07964473723101</v>
+        <v>16.67989349515331</v>
       </c>
       <c r="C3" t="n">
-        <v>35.39691347661875</v>
+        <v>22.64401079845268</v>
       </c>
       <c r="D3" t="n">
-        <v>55.11531611641593</v>
+        <v>66.78338758138928</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.77320058478576</v>
+        <v>22.18160762975243</v>
       </c>
       <c r="C4" t="n">
-        <v>54.10117073792898</v>
+        <v>55.020086589104</v>
       </c>
       <c r="D4" t="n">
-        <v>60.099649210877</v>
+        <v>52.62069519992479</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.23029410433728</v>
+        <v>20.93576979306323</v>
       </c>
       <c r="C5" t="n">
-        <v>55.86144437164352</v>
+        <v>70.41585408710249</v>
       </c>
       <c r="D5" t="n">
-        <v>38.09181092477625</v>
+        <v>33.45305302221007</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.51826497685108</v>
+        <v>11.7132318593687</v>
       </c>
       <c r="C6" t="n">
-        <v>34.85793398698726</v>
+        <v>56.51332484726341</v>
       </c>
       <c r="D6" t="n">
-        <v>32.36233132279187</v>
+        <v>30.87302005544945</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>20.12190094624263</v>
+        <v>28.02693346083794</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
         <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>31.89403766786613</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051942892444075</v>
+        <v>7.044790558113491</v>
       </c>
       <c r="C21" t="n">
-        <v>66.9934574782187</v>
+        <v>66.04491148231398</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407464307777547</v>
+        <v>4.402994098820932</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.000441968356505</v>
+        <v>4.862596379134452</v>
       </c>
       <c r="C2" t="n">
-        <v>8.459719967494765</v>
+        <v>5.610688129770521</v>
       </c>
       <c r="D2" t="n">
-        <v>23.82210804354885</v>
+        <v>32.42418142815941</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.95402208881642</v>
+        <v>19.67913273162732</v>
       </c>
       <c r="C3" t="n">
-        <v>39.28463438543612</v>
+        <v>24.09699740073796</v>
       </c>
       <c r="D3" t="n">
-        <v>64.18666490365646</v>
+        <v>71.21106972754238</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.63579696392021</v>
+        <v>28.65230674844316</v>
       </c>
       <c r="C4" t="n">
-        <v>75.91265948318036</v>
+        <v>56.16873140307276</v>
       </c>
       <c r="D4" t="n">
-        <v>74.4577093854866</v>
+        <v>75.41491339712724</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.83254741539708</v>
+        <v>28.2252464970958</v>
       </c>
       <c r="C5" t="n">
-        <v>82.90859362364314</v>
+        <v>89.31449739385359</v>
       </c>
       <c r="D5" t="n">
-        <v>52.54804586981054</v>
+        <v>45.11130701014094</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.85664913964674</v>
+        <v>20.930861054542</v>
       </c>
       <c r="C6" t="n">
-        <v>66.5762388157932</v>
+        <v>88.63414623481054</v>
       </c>
       <c r="D6" t="n">
-        <v>37.6755498981756</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.77958979262998</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>37.78845088416398</v>
+        <v>58.4493313200381</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>23.53249247079604</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.270969242753882</v>
+        <v>7.261685393844036</v>
       </c>
       <c r="C21" t="n">
-        <v>76.34517704891576</v>
+        <v>75.33998596113187</v>
       </c>
       <c r="D21" t="n">
-        <v>5.453226932065411</v>
+        <v>5.446264045383026</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.383503499462008</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C2" t="n">
-        <v>9.774280143481244</v>
+        <v>3.973132959086842</v>
       </c>
       <c r="D2" t="n">
-        <v>22.25523870757094</v>
+        <v>34.81670058340888</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.35653864755761</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="C3" t="n">
-        <v>35.46563581591602</v>
+        <v>22.73727683035613</v>
       </c>
       <c r="D3" t="n">
-        <v>68.34927516966295</v>
+        <v>80.01243789611505</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.23412328416303</v>
+        <v>34.10198825471721</v>
       </c>
       <c r="C4" t="n">
-        <v>88.93063404149306</v>
+        <v>58.00656310542279</v>
       </c>
       <c r="D4" t="n">
-        <v>89.93888893375454</v>
+        <v>92.40209392370978</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.65569395991241</v>
+        <v>35.93196597543326</v>
       </c>
       <c r="C5" t="n">
-        <v>115.0853746303324</v>
+        <v>97.4875470317083</v>
       </c>
       <c r="D5" t="n">
-        <v>67.47061097436206</v>
+        <v>61.94828013797375</v>
       </c>
     </row>
     <row r="6">
@@ -6437,10 +6437,10 @@
         <v>30.26924521733767</v>
       </c>
       <c r="C6" t="n">
-        <v>101.1121595557875</v>
+        <v>117.6153384641764</v>
       </c>
       <c r="D6" t="n">
-        <v>45.16235789076178</v>
+        <v>40.89568236810514</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.98405535702057</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>69.58824077242241</v>
+        <v>95.21970983489813</v>
       </c>
       <c r="D7" t="n">
-        <v>37.00992495469625</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>38.05254101660637</v>
+        <v>55.40984042768998</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>26.95781021091316</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -6532,7 +6532,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.4759200103965</v>
+        <v>7.46476200270576</v>
       </c>
       <c r="C21" t="n">
-        <v>85.03859011826019</v>
+        <v>83.97857253043979</v>
       </c>
       <c r="D21" t="n">
-        <v>6.541430009096938</v>
+        <v>6.531666752367539</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_60_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_60_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449764993313</v>
+        <v>10.84497645543743</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907252422223</v>
+        <v>37.78907237127503</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.361324212891832</v>
+        <v>8.801368168572655</v>
       </c>
       <c r="C2" t="n">
-        <v>4.061490252469055</v>
+        <v>8.23293624781375</v>
       </c>
       <c r="D2" t="n">
-        <v>34.9011308859741</v>
+        <v>25.14255870576081</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.38046044535803</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="C3" t="n">
-        <v>18.67775007329557</v>
+        <v>26.6397239547372</v>
       </c>
       <c r="D3" t="n">
-        <v>88.05295159389642</v>
+        <v>56.80392216772046</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.15303913533804</v>
+        <v>46.63497944713198</v>
       </c>
       <c r="C4" t="n">
-        <v>57.35566437750716</v>
+        <v>70.65441877923445</v>
       </c>
       <c r="D4" t="n">
-        <v>109.5679525324653</v>
+        <v>78.60559343592936</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.61414176116455</v>
+        <v>54.83060928218437</v>
       </c>
       <c r="C5" t="n">
-        <v>101.3899941560894</v>
+        <v>129.3698037271235</v>
       </c>
       <c r="D5" t="n">
-        <v>78.34346679889548</v>
+        <v>61.70284321191205</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.08435785376978</v>
+        <v>48.18123208132072</v>
       </c>
       <c r="C6" t="n">
-        <v>136.6543716926348</v>
+        <v>162.2544248285746</v>
       </c>
       <c r="D6" t="n">
-        <v>50.2340665309008</v>
+        <v>46.249152599363</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.82920126165683</v>
+        <v>32.45854259780804</v>
       </c>
       <c r="C7" t="n">
-        <v>131.750541909922</v>
+        <v>154.4475670844039</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>39.04606969330414</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>16.43936530761284</v>
       </c>
       <c r="C8" t="n">
-        <v>90.95892479846698</v>
+        <v>106.8975987769139</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>35.13184159647211</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>49.69999577979051</v>
+        <v>52.80624551602742</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -898,7 +898,7 @@
         <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,7 +962,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
         <v>20.78359889890498</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.18589447346791</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.653346275316912</v>
+        <v>7.638379551882944</v>
       </c>
       <c r="C21" t="n">
-        <v>92.79682358821756</v>
+        <v>92.6153520665807</v>
       </c>
       <c r="D21" t="n">
-        <v>7.653346275316912</v>
+        <v>7.638379551882944</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.723589115758905</v>
+        <v>9.056622571676826</v>
       </c>
       <c r="C2" t="n">
-        <v>11.72501283181966</v>
+        <v>15.09535270049896</v>
       </c>
       <c r="D2" t="n">
-        <v>37.16994983048848</v>
+        <v>20.20633124880785</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.94987411382118</v>
+        <v>27.25822500841269</v>
       </c>
       <c r="C3" t="n">
-        <v>17.12167996206437</v>
+        <v>29.03027961457818</v>
       </c>
       <c r="D3" t="n">
-        <v>93.3396629812655</v>
+        <v>61.89428401424016</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.26415655236718</v>
+        <v>47.11996281302991</v>
       </c>
       <c r="C4" t="n">
-        <v>51.54862670688727</v>
+        <v>67.87214578539898</v>
       </c>
       <c r="D4" t="n">
-        <v>123.5176056621082</v>
+        <v>86.07178472672636</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.80482179996669</v>
+        <v>60.94198874112077</v>
       </c>
       <c r="C5" t="n">
-        <v>102.3226544751238</v>
+        <v>129.5416095753667</v>
       </c>
       <c r="D5" t="n">
-        <v>96.28490609400595</v>
+        <v>73.55744674069228</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.85921883432777</v>
+        <v>59.65295400544471</v>
       </c>
       <c r="C6" t="n">
-        <v>148.4078552078776</v>
+        <v>180.2469150043059</v>
       </c>
       <c r="D6" t="n">
-        <v>60.33723215530473</v>
+        <v>53.09193409796327</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.99185258539232</v>
+        <v>42.93869934064274</v>
       </c>
       <c r="C7" t="n">
-        <v>161.2147540097772</v>
+        <v>190.9783991594278</v>
       </c>
       <c r="D7" t="n">
-        <v>44.31609136970101</v>
+        <v>42.99858595060179</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.36144738607885</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="C8" t="n">
-        <v>129.9293999185441</v>
+        <v>149.2894646462912</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>11.53749902030851</v>
       </c>
       <c r="C9" t="n">
-        <v>77.76718089650257</v>
+        <v>87.19686759579318</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>44.27191272300992</v>
+        <v>45.55309347705201</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.0569667290421</v>
       </c>
       <c r="D13" t="n">
         <v>33.04071898642641</v>
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.827023424925805</v>
+        <v>7.806049772520531</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7729265959197</v>
+        <v>100.5028908212018</v>
       </c>
       <c r="D21" t="n">
-        <v>8.80540135304153</v>
+        <v>8.781805994085596</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.200137662946108</v>
+        <v>12.38769253218625</v>
       </c>
       <c r="C2" t="n">
-        <v>16.42758433516188</v>
+        <v>17.621389543526</v>
       </c>
       <c r="D2" t="n">
-        <v>30.87596529856219</v>
+        <v>18.81813999500286</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.56837516749667</v>
+        <v>28.13688920371358</v>
       </c>
       <c r="C3" t="n">
-        <v>29.8402214705818</v>
+        <v>41.84699589352029</v>
       </c>
       <c r="D3" t="n">
-        <v>98.46438599743385</v>
+        <v>62.62568605390403</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.47286790274425</v>
+        <v>47.61770889908304</v>
       </c>
       <c r="C4" t="n">
-        <v>47.00509833163304</v>
+        <v>69.59511300635214</v>
       </c>
       <c r="D4" t="n">
-        <v>135.7315288506427</v>
+        <v>94.22716290590462</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.56567627075797</v>
+        <v>63.96086293167971</v>
       </c>
       <c r="C5" t="n">
-        <v>97.88024611340703</v>
+        <v>125.982774147472</v>
       </c>
       <c r="D5" t="n">
-        <v>113.6863841517807</v>
+        <v>82.95768100885549</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.73596059194917</v>
+        <v>67.94479511551327</v>
       </c>
       <c r="C6" t="n">
-        <v>154.8883718036108</v>
+        <v>189.3035375759827</v>
       </c>
       <c r="D6" t="n">
-        <v>72.05046401467342</v>
+        <v>61.46427851978007</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.31609136970101</v>
+        <v>53.59851591335461</v>
       </c>
       <c r="C7" t="n">
-        <v>182.8937068149553</v>
+        <v>218.5262397405933</v>
       </c>
       <c r="D7" t="n">
-        <v>50.06520592577034</v>
+        <v>46.71155576806323</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.78836876870596</v>
+        <v>32.87873061522568</v>
       </c>
       <c r="C8" t="n">
-        <v>164.7274472955723</v>
+        <v>192.6827131740002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.19999879422586</v>
+        <v>16.52968609640354</v>
       </c>
       <c r="C9" t="n">
-        <v>113.0453029009074</v>
+        <v>125.4703018458551</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>63.34727061652544</v>
+        <v>67.76022654711485</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.98167525545134</v>
+        <v>40.33706792438868</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.32797015314322</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.13827186204534</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1584,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1612,10 +1612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.985431263664155</v>
+        <v>7.957581393909513</v>
       </c>
       <c r="C21" t="n">
-        <v>107.8033220594661</v>
+        <v>107.4273488177784</v>
       </c>
       <c r="D21" t="n">
-        <v>9.981789079580194</v>
+        <v>9.946976742386891</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.546293691917731</v>
+        <v>11.26162791541516</v>
       </c>
       <c r="C2" t="n">
-        <v>11.30187957128928</v>
+        <v>12.4053639908627</v>
       </c>
       <c r="D2" t="n">
-        <v>25.64521353033518</v>
+        <v>15.65494889191964</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.38737373701677</v>
+        <v>32.86400439966197</v>
       </c>
       <c r="C3" t="n">
-        <v>45.47946239923349</v>
+        <v>60.19095174737195</v>
       </c>
       <c r="D3" t="n">
-        <v>105.8324025178061</v>
+        <v>68.59471209572465</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.84526907782328</v>
+        <v>30.71986741358695</v>
       </c>
       <c r="C4" t="n">
-        <v>74.12587866145118</v>
+        <v>99.62579353155782</v>
       </c>
       <c r="D4" t="n">
-        <v>129.4650332544354</v>
+        <v>90.83227934461914</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.26237298340794</v>
+        <v>38.26361677301944</v>
       </c>
       <c r="C5" t="n">
-        <v>92.55426481786806</v>
+        <v>113.0973355292326</v>
       </c>
       <c r="D5" t="n">
-        <v>73.60653412590462</v>
+        <v>58.21763886183587</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.49188096202344</v>
+        <v>33.24786775202249</v>
       </c>
       <c r="C6" t="n">
-        <v>120.4329543753648</v>
+        <v>143.9399214058504</v>
       </c>
       <c r="D6" t="n">
-        <v>32.96610616090365</v>
+        <v>30.75226508782709</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.38518925743002</v>
+        <v>21.79872602509618</v>
       </c>
       <c r="C7" t="n">
-        <v>115.8207036608132</v>
+        <v>135.4635117273834</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>27.78738702100172</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C8" t="n">
-        <v>83.28165775125692</v>
+        <v>92.46099878596459</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>26.45319189093031</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>48.36874589283183</v>
+        <v>51.69687061022852</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1881,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>24.58296251434014</v>
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
         <v>20.25247339090745</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.947607518776425</v>
+        <v>6.621888265144736</v>
       </c>
       <c r="C2" t="n">
-        <v>5.619523859108742</v>
+        <v>5.426119561372121</v>
       </c>
       <c r="D2" t="n">
-        <v>18.53441490847553</v>
+        <v>12.38572903677776</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.41820882647592</v>
+        <v>36.32466505713199</v>
       </c>
       <c r="C3" t="n">
-        <v>45.7396255408589</v>
+        <v>55.51292393663589</v>
       </c>
       <c r="D3" t="n">
-        <v>103.795276031494</v>
+        <v>65.98817194094936</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.42632485001715</v>
+        <v>44.17177445717674</v>
       </c>
       <c r="C4" t="n">
-        <v>94.62280723071608</v>
+        <v>125.5341154466311</v>
       </c>
       <c r="D4" t="n">
-        <v>147.741248516694</v>
+        <v>102.4080665253933</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.30579086657305</v>
+        <v>42.68148144213009</v>
       </c>
       <c r="C5" t="n">
-        <v>115.2080930933632</v>
+        <v>147.0658060961722</v>
       </c>
       <c r="D5" t="n">
-        <v>95.35224577497146</v>
+        <v>70.98035901704441</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.72459622565894</v>
+        <v>39.40637110076273</v>
       </c>
       <c r="C6" t="n">
-        <v>138.3046895834737</v>
+        <v>164.9110341162665</v>
       </c>
       <c r="D6" t="n">
-        <v>41.09694064747573</v>
+        <v>36.87051678069322</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.12757044828985</v>
+        <v>20.12190094624263</v>
       </c>
       <c r="C7" t="n">
-        <v>140.9730798436165</v>
+        <v>167.3830748355599</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>30.18285141936394</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>108.0658785449676</v>
+        <v>119.9155733352267</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>52.69530802544753</v>
+        <v>55.69062027110455</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2178,10 +2178,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.987859174650544</v>
+        <v>6.727917017203391</v>
       </c>
       <c r="C2" t="n">
-        <v>11.3254415161912</v>
+        <v>9.744827712353841</v>
       </c>
       <c r="D2" t="n">
-        <v>17.57132041060941</v>
+        <v>16.63178785764521</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.89726064841935</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="C3" t="n">
-        <v>33.41869185256143</v>
+        <v>38.0279973240002</v>
       </c>
       <c r="D3" t="n">
-        <v>95.30315838975912</v>
+        <v>61.63412087261476</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.42480332296516</v>
+        <v>55.88795155965818</v>
       </c>
       <c r="C4" t="n">
-        <v>104.3097118285194</v>
+        <v>131.7623228823729</v>
       </c>
       <c r="D4" t="n">
-        <v>163.1713771843411</v>
+        <v>108.9298165247048</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.92629647338604</v>
+        <v>52.79348279587224</v>
       </c>
       <c r="C5" t="n">
-        <v>143.5560580534899</v>
+        <v>187.980141670658</v>
       </c>
       <c r="D5" t="n">
-        <v>121.4421910153305</v>
+        <v>88.16094384136359</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.19882142453915</v>
+        <v>47.0944373727195</v>
       </c>
       <c r="C6" t="n">
-        <v>160.684610249484</v>
+        <v>195.5827958923453</v>
       </c>
       <c r="D6" t="n">
-        <v>57.11709968537519</v>
+        <v>47.81896717845365</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.75124228239384</v>
+        <v>30.3625112492411</v>
       </c>
       <c r="C7" t="n">
-        <v>169.598879404045</v>
+        <v>201.0393496325491</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>13.68556299720053</v>
       </c>
       <c r="C8" t="n">
-        <v>143.6984114706056</v>
+        <v>164.3102045212674</v>
       </c>
       <c r="D8" t="n">
-        <v>29.2069942013426</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>86.08749268999428</v>
+        <v>92.74374212478766</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>46.12250714551515</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.05273663858884</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.46605242207675</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.390555659840983</v>
+        <v>4.077198215737003</v>
       </c>
       <c r="C2" t="n">
-        <v>5.372123437638546</v>
+        <v>4.770312094935251</v>
       </c>
       <c r="D2" t="n">
-        <v>12.30522572502952</v>
+        <v>11.73286681345363</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.7303635386974</v>
+        <v>29.5800583289564</v>
       </c>
       <c r="C3" t="n">
-        <v>40.06512381031234</v>
+        <v>40.38910055271378</v>
       </c>
       <c r="D3" t="n">
-        <v>92.39227644666732</v>
+        <v>62.41461029749097</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.11322944782042</v>
+        <v>60.36766633413637</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6325268967673</v>
+        <v>131.8771873637698</v>
       </c>
       <c r="D4" t="n">
-        <v>173.9558757154923</v>
+        <v>115.6557700464997</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.66889864842413</v>
+        <v>53.43161880363267</v>
       </c>
       <c r="C5" t="n">
-        <v>178.4817326320702</v>
+        <v>230.6125357275758</v>
       </c>
       <c r="D5" t="n">
-        <v>128.1917064820273</v>
+        <v>90.3698761759189</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.15478164656829</v>
+        <v>37.11202671593793</v>
       </c>
       <c r="C6" t="n">
-        <v>193.8922263456323</v>
+        <v>231.5275245879338</v>
       </c>
       <c r="D6" t="n">
-        <v>55.4667817945363</v>
+        <v>46.69192081397831</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>9.042878103817369</v>
       </c>
       <c r="C7" t="n">
-        <v>182.0552942755285</v>
+        <v>210.0822277363665</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>105.6458704539993</v>
+        <v>114.9921085984289</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>30.84062238120929</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>18.8358114536793</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>22.7451308119901</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>11.82515109765283</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.18348900970292</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.159264112266236</v>
+        <v>4.704534998750716</v>
       </c>
       <c r="C2" t="n">
-        <v>9.030115383662162</v>
+        <v>3.725732537616646</v>
       </c>
       <c r="D2" t="n">
-        <v>17.8835161805599</v>
+        <v>11.64450952007142</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.1897804065559</v>
+        <v>22.23658550119026</v>
       </c>
       <c r="C3" t="n">
-        <v>30.52744486355457</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="D3" t="n">
-        <v>82.86932371547327</v>
+        <v>57.83966599570083</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.13951565165684</v>
+        <v>58.18524118759571</v>
       </c>
       <c r="C4" t="n">
-        <v>103.2759314959475</v>
+        <v>118.2721276783175</v>
       </c>
       <c r="D4" t="n">
-        <v>178.8439975349372</v>
+        <v>119.2931452907342</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.91557936409734</v>
+        <v>68.18237805994099</v>
       </c>
       <c r="C5" t="n">
-        <v>188.2010349041136</v>
+        <v>235.5212742488098</v>
       </c>
       <c r="D5" t="n">
-        <v>153.9871274111122</v>
+        <v>107.5013736150258</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.37241084174159</v>
+        <v>49.99255659565609</v>
       </c>
       <c r="C6" t="n">
-        <v>234.8281603696116</v>
+        <v>293.1528097312104</v>
       </c>
       <c r="D6" t="n">
-        <v>76.07562960208534</v>
+        <v>58.72716592033996</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>227.2097981846563</v>
+        <v>262.0638051808265</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>37.30935800449154</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>159.8874311136355</v>
+        <v>178.1626646281899</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7952820603647</v>
+        <v>32.71183350550372</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>68.67030666895162</v>
+        <v>71.88749389576842</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
         <v>23.63361248433346</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.061670178918302</v>
+        <v>3.374266859496287</v>
       </c>
       <c r="C2" t="n">
-        <v>4.693735774004001</v>
+        <v>2.861794557879453</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0955326269482</v>
+        <v>8.4793549215797</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.27184630308513</v>
+        <v>19.84602984134927</v>
       </c>
       <c r="C3" t="n">
-        <v>32.81982575297087</v>
+        <v>23.37050409959532</v>
       </c>
       <c r="D3" t="n">
-        <v>79.2270397327176</v>
+        <v>54.82570054366313</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.46385224695678</v>
+        <v>53.45027201001334</v>
       </c>
       <c r="C4" t="n">
-        <v>94.68662083149212</v>
+        <v>103.4546095781204</v>
       </c>
       <c r="D4" t="n">
-        <v>179.686337065181</v>
+        <v>120.6842817876519</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.54804586981054</v>
+        <v>75.12824306748718</v>
       </c>
       <c r="C5" t="n">
-        <v>193.2815792735908</v>
+        <v>236.9448084199677</v>
       </c>
       <c r="D5" t="n">
-        <v>172.2967220953152</v>
+        <v>119.1596276029566</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.13468902859362</v>
+        <v>58.72716592033996</v>
       </c>
       <c r="C6" t="n">
-        <v>266.7477234777882</v>
+        <v>331.5931410909943</v>
       </c>
       <c r="D6" t="n">
-        <v>90.2039608139012</v>
+        <v>68.18630505075798</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.21119892960008</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C7" t="n">
-        <v>271.4061163344392</v>
+        <v>314.8837951647134</v>
       </c>
       <c r="D7" t="n">
-        <v>44.67541102945535</v>
+        <v>41.50142070162541</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>199.9427374469054</v>
+        <v>224.893855350338</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>77.10155595302322</v>
+        <v>75.88124355664445</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.719441140763665</v>
+        <v>3.992767913171777</v>
       </c>
       <c r="C2" t="n">
-        <v>11.96652276706437</v>
+        <v>8.6491972744144</v>
       </c>
       <c r="D2" t="n">
-        <v>22.19829734072463</v>
+        <v>11.92136237266902</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.76348091873453</v>
+        <v>15.87976911619216</v>
       </c>
       <c r="C3" t="n">
-        <v>26.03104037810418</v>
+        <v>18.04452280405637</v>
       </c>
       <c r="D3" t="n">
-        <v>73.26292242941823</v>
+        <v>50.01022805433252</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.89479843139213</v>
+        <v>46.36696232387261</v>
       </c>
       <c r="C4" t="n">
-        <v>88.85405772056183</v>
+        <v>83.49371525537424</v>
       </c>
       <c r="D4" t="n">
-        <v>176.0234363806361</v>
+        <v>119.9440440186498</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.51721078035138</v>
+        <v>76.42905877561419</v>
       </c>
       <c r="C5" t="n">
-        <v>184.8385490170683</v>
+        <v>217.4080291054562</v>
       </c>
       <c r="D5" t="n">
-        <v>190.3363361608504</v>
+        <v>128.4862307933013</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.6680400739069</v>
+        <v>73.13725872327464</v>
       </c>
       <c r="C6" t="n">
-        <v>283.3314056979253</v>
+        <v>349.7063862343479</v>
       </c>
       <c r="D6" t="n">
-        <v>113.0266496945268</v>
+        <v>83.15992103593032</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.14670668075605</v>
+        <v>33.17718191731671</v>
       </c>
       <c r="C7" t="n">
-        <v>319.4351775216017</v>
+        <v>380.7590661196745</v>
       </c>
       <c r="D7" t="n">
-        <v>54.73636150257666</v>
+        <v>48.08894779712151</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.760715602071035</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>259.1912113982004</v>
+        <v>293.9058102203676</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>136.8968633755837</v>
+        <v>144.3296752444363</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>51.24723016168351</v>
+        <v>49.68134257340984</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.546874528994478</v>
+        <v>7.269841749947631</v>
       </c>
       <c r="C2" t="n">
-        <v>11.60818485501428</v>
+        <v>12.82358851287184</v>
       </c>
       <c r="D2" t="n">
-        <v>9.469938355164732</v>
+        <v>14.11949548247763</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.988039101099791</v>
+        <v>2.955060589782899</v>
       </c>
       <c r="C2" t="n">
-        <v>6.988080158828796</v>
+        <v>5.119814277647116</v>
       </c>
       <c r="D2" t="n">
-        <v>16.51495988083985</v>
+        <v>8.869108760165686</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.9885221271853</v>
+        <v>20.88177366932966</v>
       </c>
       <c r="C3" t="n">
-        <v>35.99087083768807</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D3" t="n">
-        <v>81.74522259411067</v>
+        <v>54.88951414443918</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.51338160052563</v>
+        <v>60.04859833025616</v>
       </c>
       <c r="C4" t="n">
-        <v>121.6542485194477</v>
+        <v>120.9395361907561</v>
       </c>
       <c r="D4" t="n">
-        <v>179.2141164194383</v>
+        <v>121.9605538031728</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.83316931020283</v>
+        <v>41.89608327873264</v>
       </c>
       <c r="C5" t="n">
-        <v>255.9416264971435</v>
+        <v>309.1032646821083</v>
       </c>
       <c r="D5" t="n">
-        <v>171.4867802393116</v>
+        <v>117.8342682022234</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.46921864936775</v>
+        <v>20.56859615167493</v>
       </c>
       <c r="C6" t="n">
-        <v>260.3477101938032</v>
+        <v>309.0522138014875</v>
       </c>
       <c r="D6" t="n">
-        <v>85.61527204425161</v>
+        <v>67.78378849201678</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>182.2349541054057</v>
+        <v>206.6686909687003</v>
       </c>
       <c r="D7" t="n">
-        <v>32.75797564760332</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>100.8893028269235</v>
+        <v>106.3134588928871</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>23.86628669023996</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.2218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>37.94062177832222</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>19.96874830438012</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>20.4988920646734</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>18.79065105928395</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>12.80100831567416</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.018113427032947</v>
+        <v>7.315983892047231</v>
       </c>
       <c r="C2" t="n">
-        <v>5.673519982842318</v>
+        <v>8.94470333339269</v>
       </c>
       <c r="D2" t="n">
-        <v>22.81188965587889</v>
+        <v>14.03899217072939</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.78588118948296</v>
+        <v>15.43798264928109</v>
       </c>
       <c r="C3" t="n">
-        <v>29.25117284803371</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D3" t="n">
-        <v>11.08884031946772</v>
+        <v>14.99619618237003</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4585,7 +4585,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="D7" t="n">
         <v>32.21899615797182</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39743156710496</v>
+        <v>13.39613299420829</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13949467484359</v>
+        <v>70.13269626379635</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576168419659406</v>
+        <v>1.576015646377446</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.05698242457532</v>
+        <v>6.245878894418207</v>
       </c>
       <c r="C2" t="n">
-        <v>6.8791061636574</v>
+        <v>8.101382055444679</v>
       </c>
       <c r="D2" t="n">
-        <v>26.17437554292421</v>
+        <v>19.32668530580271</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.19531103988288</v>
+        <v>21.36773878293183</v>
       </c>
       <c r="C3" t="n">
-        <v>24.7940382707532</v>
+        <v>33.9193831817273</v>
       </c>
       <c r="D3" t="n">
-        <v>27.56747553525044</v>
+        <v>23.16433708170349</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.74544960715959</v>
+        <v>17.86780821729195</v>
       </c>
       <c r="C4" t="n">
-        <v>45.11621574866217</v>
+        <v>49.78737132546849</v>
       </c>
       <c r="D4" t="n">
-        <v>20.87981017392116</v>
+        <v>22.93460811890974</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.58368222013712</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4896,7 +4896,7 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4910,10 +4910,10 @@
         <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43712017374265</v>
+        <v>15.43457365470526</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12288096930109</v>
+        <v>86.1086740736188</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2499200365774</v>
+        <v>3.24938392730637</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.568072067860409</v>
+        <v>6.021058670145687</v>
       </c>
       <c r="C2" t="n">
-        <v>7.67628529950581</v>
+        <v>5.957245069369645</v>
       </c>
       <c r="D2" t="n">
-        <v>33.26946620151591</v>
+        <v>16.34708102341364</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5291052593268</v>
+        <v>21.45609607631404</v>
       </c>
       <c r="C3" t="n">
-        <v>25.95250056176443</v>
+        <v>32.47130531796326</v>
       </c>
       <c r="D3" t="n">
-        <v>42.1071590351457</v>
+        <v>33.24688600431823</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.47889725768997</v>
+        <v>30.78368101436299</v>
       </c>
       <c r="C4" t="n">
-        <v>54.94351026817274</v>
+        <v>70.13114725287089</v>
       </c>
       <c r="D4" t="n">
-        <v>29.99239236474006</v>
+        <v>29.39254451744526</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.12458414744811</v>
+        <v>15.31526418625024</v>
       </c>
       <c r="C5" t="n">
-        <v>48.98921044191585</v>
+        <v>53.8979489631499</v>
       </c>
       <c r="D5" t="n">
-        <v>30.16419821298325</v>
+        <v>31.17048960983623</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.31700669748049</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.39663573917827</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72422386260005</v>
+        <v>16.71871017950435</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0177655618603</v>
+        <v>101.1481965860013</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181055965650012</v>
+        <v>4.179677544876087</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.053456344385832</v>
+        <v>7.462264299980006</v>
       </c>
       <c r="C2" t="n">
-        <v>5.430046552189108</v>
+        <v>10.52237189411731</v>
       </c>
       <c r="D2" t="n">
-        <v>33.31069960509427</v>
+        <v>21.68778853451629</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.46881773874025</v>
+        <v>20.9455872701057</v>
       </c>
       <c r="C3" t="n">
-        <v>28.09761929554371</v>
+        <v>27.13059780686061</v>
       </c>
       <c r="D3" t="n">
-        <v>58.02619805950773</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.53293443915255</v>
+        <v>36.53966780436203</v>
       </c>
       <c r="C4" t="n">
-        <v>60.40595449460199</v>
+        <v>76.21896476690537</v>
       </c>
       <c r="D4" t="n">
-        <v>43.57192660988194</v>
+        <v>38.90077103307561</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.02827506144069</v>
+        <v>30.23782929080177</v>
       </c>
       <c r="C5" t="n">
-        <v>76.33088400518952</v>
+        <v>93.95325529641977</v>
       </c>
       <c r="D5" t="n">
-        <v>33.69848994827177</v>
+        <v>34.5820628820939</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.10945702125691</v>
+        <v>13.20254312671111</v>
       </c>
       <c r="C6" t="n">
-        <v>46.08814597586652</v>
+        <v>49.30827844579606</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>37.6755498981756</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.37951975538279</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.2097595180061</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.72499713628642</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>48.82722207071512</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.28806265463436</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03854078209885</v>
+        <v>18.03036294970879</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6800041498829</v>
+        <v>116.7680648171617</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012846927366281</v>
+        <v>6.010120983236263</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.183047041346412</v>
+        <v>8.52255182056656</v>
       </c>
       <c r="C2" t="n">
-        <v>6.387250563829748</v>
+        <v>8.22115527536279</v>
       </c>
       <c r="D2" t="n">
-        <v>24.48282424850696</v>
+        <v>23.34399691158066</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.67989349515331</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="C3" t="n">
-        <v>22.64401079845268</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D3" t="n">
-        <v>66.78338758138928</v>
+        <v>42.98582323044659</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.18160762975243</v>
+        <v>28.07798434145878</v>
       </c>
       <c r="C4" t="n">
-        <v>55.020086589104</v>
+        <v>59.23178424032281</v>
       </c>
       <c r="D4" t="n">
-        <v>52.62069519992479</v>
+        <v>41.63199314629023</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.93576979306323</v>
+        <v>25.6727024660541</v>
       </c>
       <c r="C5" t="n">
-        <v>70.41585408710249</v>
+        <v>88.01368168572657</v>
       </c>
       <c r="D5" t="n">
-        <v>33.45305302221007</v>
+        <v>32.7658296292373</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.7132318593687</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="C6" t="n">
-        <v>56.51332484726341</v>
+        <v>67.01900703040852</v>
       </c>
       <c r="D6" t="n">
-        <v>30.87302005544945</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>28.02693346083794</v>
+        <v>29.52409870981433</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.52187317249857</v>
       </c>
       <c r="D9" t="n">
         <v>30.17499743772996</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>31.89403766786613</v>
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.044790558113491</v>
+        <v>7.03988931668193</v>
       </c>
       <c r="C21" t="n">
-        <v>66.04491148231398</v>
+        <v>65.9989623438931</v>
       </c>
       <c r="D21" t="n">
-        <v>4.402994098820932</v>
+        <v>4.399930822926206</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.862596379134452</v>
+        <v>7.792131528606935</v>
       </c>
       <c r="C2" t="n">
-        <v>5.610688129770521</v>
+        <v>5.541965790473244</v>
       </c>
       <c r="D2" t="n">
-        <v>32.42418142815941</v>
+        <v>20.16902483604647</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.67913273162732</v>
+        <v>26.07031028627405</v>
       </c>
       <c r="C3" t="n">
-        <v>24.09699740073796</v>
+        <v>32.23077713042279</v>
       </c>
       <c r="D3" t="n">
-        <v>71.21106972754238</v>
+        <v>52.20934291184538</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.65230674844316</v>
+        <v>35.46759931132452</v>
       </c>
       <c r="C4" t="n">
-        <v>56.16873140307276</v>
+        <v>72.24975879863551</v>
       </c>
       <c r="D4" t="n">
-        <v>75.41491339712724</v>
+        <v>54.49681506274044</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.2252464970958</v>
+        <v>35.31837366027901</v>
       </c>
       <c r="C5" t="n">
-        <v>89.31449739385359</v>
+        <v>101.0954698448153</v>
       </c>
       <c r="D5" t="n">
-        <v>45.11130701014094</v>
+        <v>40.5216364927871</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.930861054542</v>
+        <v>25.88181472705867</v>
       </c>
       <c r="C6" t="n">
-        <v>88.63414623481054</v>
+        <v>109.2429940423596</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>34.65667570761666</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.30049691295753</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>58.4493313200381</v>
+        <v>67.97130230352791</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>30.45872252425729</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
         <v>31.39530983410874</v>
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.05772749256809</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,10 +6305,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.261685393844036</v>
+        <v>7.254210613145432</v>
       </c>
       <c r="C21" t="n">
-        <v>75.33998596113187</v>
+        <v>75.26243511138387</v>
       </c>
       <c r="D21" t="n">
-        <v>5.446264045383026</v>
+        <v>5.440657959859074</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.412955930589413</v>
+        <v>7.678248794914303</v>
       </c>
       <c r="C2" t="n">
-        <v>3.973132959086842</v>
+        <v>7.062692984351554</v>
       </c>
       <c r="D2" t="n">
-        <v>34.81670058340888</v>
+        <v>17.74999849278233</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.05434028109884</v>
+        <v>26.41883072128167</v>
       </c>
       <c r="C3" t="n">
-        <v>22.73727683035613</v>
+        <v>25.93777434620073</v>
       </c>
       <c r="D3" t="n">
-        <v>80.01243789611505</v>
+        <v>55.92525797241955</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.10198825471721</v>
+        <v>43.45706212848506</v>
       </c>
       <c r="C4" t="n">
-        <v>58.00656310542279</v>
+        <v>77.06130429714914</v>
       </c>
       <c r="D4" t="n">
-        <v>92.40209392370978</v>
+        <v>67.13190801639689</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.93196597543326</v>
+        <v>44.98858854711009</v>
       </c>
       <c r="C5" t="n">
-        <v>97.4875470317083</v>
+        <v>118.9632780621073</v>
       </c>
       <c r="D5" t="n">
-        <v>61.94828013797375</v>
+        <v>51.00179323562181</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.26924521733767</v>
+        <v>37.15227837181205</v>
       </c>
       <c r="C6" t="n">
-        <v>117.6153384641764</v>
+        <v>135.7285836075301</v>
       </c>
       <c r="D6" t="n">
-        <v>40.89568236810514</v>
+        <v>39.64788103600744</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.84620976779852</v>
+        <v>21.91849924501429</v>
       </c>
       <c r="C7" t="n">
-        <v>95.21970983489813</v>
+        <v>116.1201367106085</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>55.40984042768998</v>
+        <v>61.91882770684633</v>
       </c>
       <c r="D8" t="n">
         <v>33.46287049925253</v>
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
         <v>32.28280975874785</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.84673385161303</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.46476200270576</v>
+        <v>7.454093785021173</v>
       </c>
       <c r="C21" t="n">
-        <v>83.97857253043979</v>
+        <v>83.85855508148821</v>
       </c>
       <c r="D21" t="n">
-        <v>6.531666752367539</v>
+        <v>6.522332061893526</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_60_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_60_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497645543743</v>
+        <v>10.84497650362522</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907237127503</v>
+        <v>37.78907253918426</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.801368168572655</v>
+        <v>1.028871594050657</v>
       </c>
       <c r="C2" t="n">
-        <v>8.23293624781375</v>
+        <v>1.932079481957723</v>
       </c>
       <c r="D2" t="n">
-        <v>25.14255870576081</v>
+        <v>18.27327001914588</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.03594911662541</v>
+        <v>11.04957041129785</v>
       </c>
       <c r="C3" t="n">
-        <v>26.6397239547372</v>
+        <v>23.85646921319749</v>
       </c>
       <c r="D3" t="n">
-        <v>56.80392216772046</v>
+        <v>88.88743714250622</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.63497944713198</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="C4" t="n">
-        <v>70.65441877923445</v>
+        <v>86.45466633138263</v>
       </c>
       <c r="D4" t="n">
-        <v>78.60559343592936</v>
+        <v>96.84352053772237</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.83060928218437</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="C5" t="n">
-        <v>129.3698037271235</v>
+        <v>116.5825398793088</v>
       </c>
       <c r="D5" t="n">
-        <v>61.70284321191205</v>
+        <v>52.64622064023522</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.18123208132072</v>
+        <v>11.39121861237574</v>
       </c>
       <c r="C6" t="n">
-        <v>162.2544248285746</v>
+        <v>72.33222560579226</v>
       </c>
       <c r="D6" t="n">
-        <v>46.249152599363</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.45854259780804</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>154.4475670844039</v>
+        <v>36.11162580531042</v>
       </c>
       <c r="D7" t="n">
-        <v>39.04606969330414</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.43936530761284</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>106.8975987769139</v>
+        <v>28.03871443328891</v>
       </c>
       <c r="D8" t="n">
-        <v>35.13184159647211</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>52.80624551602742</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.18589447346791</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.638379551882944</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.6153520665807</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.638379551882944</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.056622571676826</v>
+        <v>1.235038611942487</v>
       </c>
       <c r="C2" t="n">
-        <v>15.09535270049896</v>
+        <v>7.800967257945155</v>
       </c>
       <c r="D2" t="n">
-        <v>20.20633124880785</v>
+        <v>17.30624853046277</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.25822500841269</v>
+        <v>7.01458734684346</v>
       </c>
       <c r="C3" t="n">
-        <v>29.03027961457818</v>
+        <v>14.25006792714245</v>
       </c>
       <c r="D3" t="n">
-        <v>61.89428401424016</v>
+        <v>83.00185965554658</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.11996281302991</v>
+        <v>20.85428473361074</v>
       </c>
       <c r="C4" t="n">
-        <v>67.87214578539898</v>
+        <v>72.10936887692823</v>
       </c>
       <c r="D4" t="n">
-        <v>86.07178472672636</v>
+        <v>118.3869921597144</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.94198874112077</v>
+        <v>23.34105166846792</v>
       </c>
       <c r="C5" t="n">
-        <v>129.5416095753667</v>
+        <v>139.8990478551705</v>
       </c>
       <c r="D5" t="n">
-        <v>73.55744674069228</v>
+        <v>74.12195167063419</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.65295400544471</v>
+        <v>17.02645043475243</v>
       </c>
       <c r="C6" t="n">
-        <v>180.2469150043059</v>
+        <v>131.5826630524958</v>
       </c>
       <c r="D6" t="n">
-        <v>53.09193409796327</v>
+        <v>39.16486116551801</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.93869934064274</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>190.9783991594278</v>
+        <v>70.78597297160351</v>
       </c>
       <c r="D7" t="n">
-        <v>42.99858595060179</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.36697801940583</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>149.2894646462912</v>
+        <v>38.55323234577224</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.53749902030851</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>87.19686759579318</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>45.55309347705201</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.0569667290421</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.806049772520531</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.5028908212018</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.781805994085596</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12.38769253218625</v>
+        <v>0.6587527095496097</v>
       </c>
       <c r="C2" t="n">
-        <v>17.621389543526</v>
+        <v>3.199515768140355</v>
       </c>
       <c r="D2" t="n">
-        <v>18.81813999500286</v>
+        <v>11.67494369890307</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.13688920371358</v>
+        <v>6.518804756198822</v>
       </c>
       <c r="C3" t="n">
-        <v>41.84699589352029</v>
+        <v>23.36068662255285</v>
       </c>
       <c r="D3" t="n">
-        <v>62.62568605390403</v>
+        <v>81.19544387973247</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.61770889908304</v>
+        <v>22.39857387239098</v>
       </c>
       <c r="C4" t="n">
-        <v>69.59511300635214</v>
+        <v>64.41344862333747</v>
       </c>
       <c r="D4" t="n">
-        <v>94.22716290590462</v>
+        <v>132.8216286552552</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.96086293167971</v>
+        <v>23.21833320543707</v>
       </c>
       <c r="C5" t="n">
-        <v>125.982774147472</v>
+        <v>156.7851083682156</v>
       </c>
       <c r="D5" t="n">
-        <v>82.95768100885549</v>
+        <v>84.184865639164</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.94479511551327</v>
+        <v>13.56480802957818</v>
       </c>
       <c r="C6" t="n">
-        <v>189.3035375759827</v>
+        <v>165.756318889623</v>
       </c>
       <c r="D6" t="n">
-        <v>61.46427851978007</v>
+        <v>39.60762938013333</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.59851591335461</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>218.5262397405933</v>
+        <v>67.97130230352791</v>
       </c>
       <c r="D7" t="n">
-        <v>46.71155576806323</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.87873061522568</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>192.6827131740002</v>
+        <v>38.63668090063322</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.52968609640354</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>125.4703018458551</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>67.76022654711485</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>40.33706792438868</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.32797015314322</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.957581393909513</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.4273488177784</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.946976742386891</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.26162791541516</v>
+        <v>1.145699570856028</v>
       </c>
       <c r="C2" t="n">
-        <v>12.4053639908627</v>
+        <v>3.834706532788041</v>
       </c>
       <c r="D2" t="n">
-        <v>15.65494889191964</v>
+        <v>10.03247978969815</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>32.86400439966197</v>
+        <v>4.319689898685966</v>
       </c>
       <c r="C3" t="n">
-        <v>60.19095174737195</v>
+        <v>17.25421590213769</v>
       </c>
       <c r="D3" t="n">
-        <v>68.59471209572465</v>
+        <v>72.78677479285852</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.71986741358695</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="C4" t="n">
-        <v>99.62579353155782</v>
+        <v>61.74604011089889</v>
       </c>
       <c r="D4" t="n">
-        <v>90.83227934461914</v>
+        <v>142.3043297305751</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.26361677301944</v>
+        <v>28.397052345339</v>
       </c>
       <c r="C5" t="n">
-        <v>113.0973355292326</v>
+        <v>138.5982321470435</v>
       </c>
       <c r="D5" t="n">
-        <v>58.21763886183587</v>
+        <v>109.5630437939441</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.24786775202249</v>
+        <v>21.29312595740907</v>
       </c>
       <c r="C6" t="n">
-        <v>143.9399214058504</v>
+        <v>210.2746502863989</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>54.58124536530568</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.79872602509618</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
-        <v>135.4635117273834</v>
+        <v>148.039699818785</v>
       </c>
       <c r="D7" t="n">
-        <v>27.78738702100172</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>92.46099878596459</v>
+        <v>61.83537915198535</v>
       </c>
       <c r="D8" t="n">
-        <v>26.45319189093031</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>51.69687061022852</v>
+        <v>36.16562192904399</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>23.65030219530566</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.5585576904542</v>
-      </c>
-      <c r="D15" t="n">
-        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.621888265144736</v>
+        <v>0.5723589115758905</v>
       </c>
       <c r="C2" t="n">
-        <v>5.426119561372121</v>
+        <v>2.359139733305085</v>
       </c>
       <c r="D2" t="n">
-        <v>12.38572903677776</v>
+        <v>8.097455064627692</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>36.32466505713199</v>
+        <v>4.221515128261284</v>
       </c>
       <c r="C3" t="n">
-        <v>55.51292393663589</v>
+        <v>16.26755945936965</v>
       </c>
       <c r="D3" t="n">
-        <v>65.98817194094936</v>
+        <v>65.51693304291089</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.17177445717674</v>
+        <v>14.25595841336793</v>
       </c>
       <c r="C4" t="n">
-        <v>125.5341154466311</v>
+        <v>54.29261154025711</v>
       </c>
       <c r="D4" t="n">
-        <v>102.4080665253933</v>
+        <v>146.5543155422596</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.68148144213009</v>
+        <v>29.67332436085985</v>
       </c>
       <c r="C5" t="n">
-        <v>147.0658060961722</v>
+        <v>132.6341148437441</v>
       </c>
       <c r="D5" t="n">
-        <v>70.98035901704441</v>
+        <v>130.3760951239765</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.40637110076273</v>
+        <v>26.64659618866693</v>
       </c>
       <c r="C6" t="n">
-        <v>164.9110341162665</v>
+        <v>227.1400940976548</v>
       </c>
       <c r="D6" t="n">
-        <v>36.87051678069322</v>
+        <v>68.70957657712154</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.12190094624263</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="C7" t="n">
-        <v>167.3830748355599</v>
+        <v>206.5489177487822</v>
       </c>
       <c r="D7" t="n">
-        <v>30.18285141936394</v>
+        <v>40.18391528252619</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>119.9155733352267</v>
+        <v>97.55136063248432</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>55.69062027110455</v>
+        <v>46.70468353413349</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.727917017203391</v>
+        <v>0.8472482687649974</v>
       </c>
       <c r="C2" t="n">
-        <v>9.744827712353841</v>
+        <v>9.158724332918494</v>
       </c>
       <c r="D2" t="n">
-        <v>16.63178785764521</v>
+        <v>13.39103868592649</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.42788743479814</v>
+        <v>3.082687791334985</v>
       </c>
       <c r="C3" t="n">
-        <v>38.0279973240002</v>
+        <v>12.46328710541326</v>
       </c>
       <c r="D3" t="n">
-        <v>61.63412087261476</v>
+        <v>57.70713005562752</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.88795155965818</v>
+        <v>11.23119373658351</v>
       </c>
       <c r="C4" t="n">
-        <v>131.7623228823729</v>
+        <v>47.80914970141117</v>
       </c>
       <c r="D4" t="n">
-        <v>108.9298165247048</v>
+        <v>145.9799931352752</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.79348279587224</v>
+        <v>26.65445017030091</v>
       </c>
       <c r="C5" t="n">
-        <v>187.980141670658</v>
+        <v>116.8525204979766</v>
       </c>
       <c r="D5" t="n">
-        <v>88.16094384136359</v>
+        <v>149.6674375124263</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.0944373727195</v>
+        <v>32.6440929139107</v>
       </c>
       <c r="C6" t="n">
-        <v>195.5827958923453</v>
+        <v>220.6998291577958</v>
       </c>
       <c r="D6" t="n">
-        <v>47.81896717845365</v>
+        <v>88.67439789068467</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.3625112492411</v>
+        <v>18.56484908730718</v>
       </c>
       <c r="C7" t="n">
-        <v>201.0393496325491</v>
+        <v>265.1180222887384</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>48.26860762699867</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>164.3102045212674</v>
+        <v>174.9081709886117</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>41.64082887562846</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>92.74374212478766</v>
+        <v>77.98905587766234</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>42.59999638267758</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>46.12250714551515</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.077198215737003</v>
+        <v>0.5684319207589033</v>
       </c>
       <c r="C2" t="n">
-        <v>4.770312094935251</v>
+        <v>4.762458113301277</v>
       </c>
       <c r="D2" t="n">
-        <v>11.73286681345363</v>
+        <v>9.640762455703678</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.5800583289564</v>
+        <v>4.344233591292136</v>
       </c>
       <c r="C3" t="n">
-        <v>40.38910055271378</v>
+        <v>22.75200304591983</v>
       </c>
       <c r="D3" t="n">
-        <v>62.41461029749097</v>
+        <v>63.44544538695013</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>60.36766633413637</v>
+        <v>18.28897798241383</v>
       </c>
       <c r="C4" t="n">
-        <v>131.8771873637698</v>
+        <v>66.92770449391357</v>
       </c>
       <c r="D4" t="n">
-        <v>115.6557700464997</v>
+        <v>150.3065552678909</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.43161880363267</v>
+        <v>20.34672117051515</v>
       </c>
       <c r="C5" t="n">
-        <v>230.6125357275758</v>
+        <v>180.7888397370502</v>
       </c>
       <c r="D5" t="n">
-        <v>90.3698761759189</v>
+        <v>136.0456881160018</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.11202671593793</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="C6" t="n">
-        <v>231.5275245879338</v>
+        <v>228.6696570208714</v>
       </c>
       <c r="D6" t="n">
-        <v>46.69192081397831</v>
+        <v>72.2114706381699</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.042878103817369</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>210.0822277363665</v>
+        <v>123.0070968558999</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>114.9921085984289</v>
+        <v>57.41260574435346</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>35.16718451382499</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>18.8358114536793</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>22.7451308119901</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.704534998750716</v>
+        <v>0.3337942194439155</v>
       </c>
       <c r="C2" t="n">
-        <v>3.725732537616646</v>
+        <v>2.84706834231575</v>
       </c>
       <c r="D2" t="n">
-        <v>11.64450952007142</v>
+        <v>6.94684675525043</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.23658550119026</v>
+        <v>3.126866438026091</v>
       </c>
       <c r="C3" t="n">
-        <v>29.70768553050848</v>
+        <v>20.49398332615217</v>
       </c>
       <c r="D3" t="n">
-        <v>57.83966599570083</v>
+        <v>56.70083865877454</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>58.18524118759571</v>
+        <v>12.53299119241478</v>
       </c>
       <c r="C4" t="n">
-        <v>118.2721276783175</v>
+        <v>59.74229304653115</v>
       </c>
       <c r="D4" t="n">
-        <v>119.2931452907342</v>
+        <v>142.2532788499543</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.18237805994099</v>
+        <v>19.02136176978195</v>
       </c>
       <c r="C5" t="n">
-        <v>235.5212742488098</v>
+        <v>137.2974164389165</v>
       </c>
       <c r="D5" t="n">
-        <v>107.5013736150258</v>
+        <v>142.3779608083937</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.99255659565609</v>
+        <v>11.63272854762046</v>
       </c>
       <c r="C6" t="n">
-        <v>293.1528097312104</v>
+        <v>214.4205708414332</v>
       </c>
       <c r="D6" t="n">
-        <v>58.72716592033996</v>
+        <v>78.28947067516191</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.40326162673396</v>
+        <v>3.832743037379548</v>
       </c>
       <c r="C7" t="n">
-        <v>262.0638051808265</v>
+        <v>156.1842787732166</v>
       </c>
       <c r="D7" t="n">
-        <v>37.30935800449154</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>178.1626646281899</v>
+        <v>66.00780689503429</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>71.88749389576842</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>18.64829764216817</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.374266859496287</v>
+        <v>0.4162610266006476</v>
       </c>
       <c r="C2" t="n">
-        <v>2.861794557879453</v>
+        <v>4.637776154861932</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4793549215797</v>
+        <v>14.01837546894021</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.84602984134927</v>
+        <v>2.037126486312132</v>
       </c>
       <c r="C3" t="n">
-        <v>23.37050409959532</v>
+        <v>14.98146996680633</v>
       </c>
       <c r="D3" t="n">
-        <v>54.82570054366313</v>
+        <v>49.10211142790422</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.45027201001334</v>
+        <v>9.189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>103.4546095781204</v>
+        <v>54.89245938755191</v>
       </c>
       <c r="D4" t="n">
-        <v>120.6842817876519</v>
+        <v>138.9094461692897</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>75.12824306748718</v>
+        <v>19.24225500323749</v>
       </c>
       <c r="C5" t="n">
-        <v>236.9448084199677</v>
+        <v>122.3748513343649</v>
       </c>
       <c r="D5" t="n">
-        <v>119.1596276029566</v>
+        <v>161.9638275081176</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.72716592033996</v>
+        <v>18.8377749490878</v>
       </c>
       <c r="C6" t="n">
-        <v>331.5931410909943</v>
+        <v>219.6532861050686</v>
       </c>
       <c r="D6" t="n">
-        <v>68.18630505075798</v>
+        <v>104.0102787787241</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.18745705824891</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>314.8837951647134</v>
+        <v>239.0074603465902</v>
       </c>
       <c r="D7" t="n">
-        <v>41.50142070162541</v>
+        <v>48.98724694650735</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>224.893855350338</v>
+        <v>137.9404611851981</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>75.88124355664445</v>
+        <v>55.69062027110455</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>23.51874800293658</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>17.59193711239859</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.992767913171777</v>
+        <v>0.5527239574909543</v>
       </c>
       <c r="C2" t="n">
-        <v>8.6491972744144</v>
+        <v>9.891108120286614</v>
       </c>
       <c r="D2" t="n">
-        <v>11.92136237266902</v>
+        <v>17.2983945488288</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.87976911619216</v>
+        <v>1.703332266868216</v>
       </c>
       <c r="C3" t="n">
-        <v>18.04452280405637</v>
+        <v>16.63080610994097</v>
       </c>
       <c r="D3" t="n">
-        <v>50.01022805433252</v>
+        <v>48.74377351585414</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.36696232387261</v>
+        <v>6.483461838845936</v>
       </c>
       <c r="C4" t="n">
-        <v>83.49371525537424</v>
+        <v>45.48633463316322</v>
       </c>
       <c r="D4" t="n">
-        <v>119.9440440186498</v>
+        <v>131.4049667180271</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>76.42905877561419</v>
+        <v>16.95969159086365</v>
       </c>
       <c r="C5" t="n">
-        <v>217.4080291054562</v>
+        <v>111.428364432013</v>
       </c>
       <c r="D5" t="n">
-        <v>128.4862307933013</v>
+        <v>175.1928778228433</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73.13725872327464</v>
+        <v>22.54092728950677</v>
       </c>
       <c r="C6" t="n">
-        <v>349.7063862343479</v>
+        <v>208.2620674926929</v>
       </c>
       <c r="D6" t="n">
-        <v>83.15992103593032</v>
+        <v>128.966305420678</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.17718191731671</v>
+        <v>15.09142570968197</v>
       </c>
       <c r="C7" t="n">
-        <v>380.7590661196745</v>
+        <v>280.2094479984203</v>
       </c>
       <c r="D7" t="n">
-        <v>48.08894779712151</v>
+        <v>64.55776553586176</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>293.9058102203676</v>
+        <v>225.8117894538088</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>144.3296752444363</v>
+        <v>110.7156155987298</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>25.62656032395449</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>49.68134257340984</v>
+        <v>45.12603322570465</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.269841749947631</v>
+        <v>4.05658151394782</v>
       </c>
       <c r="C2" t="n">
-        <v>12.82358851287184</v>
+        <v>6.247842389826701</v>
       </c>
       <c r="D2" t="n">
-        <v>14.11949548247763</v>
+        <v>9.939213757794709</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.955060589782899</v>
+        <v>0.9552405162321465</v>
       </c>
       <c r="C2" t="n">
-        <v>5.119814277647116</v>
+        <v>9.337402415091415</v>
       </c>
       <c r="D2" t="n">
-        <v>8.869108760165686</v>
+        <v>20.78556239431347</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.88177366932966</v>
+        <v>1.762237129123025</v>
       </c>
       <c r="C3" t="n">
-        <v>25.23582473766426</v>
+        <v>27.52820562708057</v>
       </c>
       <c r="D3" t="n">
-        <v>54.88951414443918</v>
+        <v>50.59927667688061</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>60.04859833025616</v>
+        <v>4.913647259755287</v>
       </c>
       <c r="C4" t="n">
-        <v>120.9395361907561</v>
+        <v>43.48258756879548</v>
       </c>
       <c r="D4" t="n">
-        <v>121.9605538031728</v>
+        <v>126.6444721001343</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.89608327873264</v>
+        <v>13.84264262988003</v>
       </c>
       <c r="C5" t="n">
-        <v>309.1032646821083</v>
+        <v>97.21756641304043</v>
       </c>
       <c r="D5" t="n">
-        <v>117.8342682022234</v>
+        <v>181.770587441297</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.56859615167493</v>
+        <v>23.06419881587032</v>
       </c>
       <c r="C6" t="n">
-        <v>309.0522138014875</v>
+        <v>194.9790210542336</v>
       </c>
       <c r="D6" t="n">
-        <v>67.78378849201678</v>
+        <v>148.7701201107447</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>20.18178755620168</v>
       </c>
       <c r="C7" t="n">
-        <v>206.6686909687003</v>
+        <v>292.845522699781</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>82.58363513353744</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>106.3134588928871</v>
+        <v>291.2354564648163</v>
       </c>
       <c r="D8" t="n">
-        <v>23.86628669023996</v>
+        <v>42.39186586937727</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94062177832222</v>
+        <v>186.7077966459541</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>20.4988920646734</v>
+        <v>82.13792167580941</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>22.49183990429443</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>35.18387422479719</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.315983892047231</v>
+        <v>5.079562621772997</v>
       </c>
       <c r="C2" t="n">
-        <v>8.94470333339269</v>
+        <v>10.81493270998286</v>
       </c>
       <c r="D2" t="n">
-        <v>14.03899217072939</v>
+        <v>25.03554820599791</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.43798264928109</v>
+        <v>6.705336820005716</v>
       </c>
       <c r="C3" t="n">
-        <v>32.31422568528377</v>
+        <v>12.33565990386117</v>
       </c>
       <c r="D3" t="n">
-        <v>14.99619618237003</v>
+        <v>9.81256830394687</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39613299420829</v>
+        <v>11.67838581028603</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13269626379635</v>
+        <v>59.9490471594683</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576015646377446</v>
+        <v>0.7785590540190689</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.245878894418207</v>
+        <v>2.63795608131118</v>
       </c>
       <c r="C2" t="n">
-        <v>8.101382055444679</v>
+        <v>7.918776982454772</v>
       </c>
       <c r="D2" t="n">
-        <v>19.32668530580271</v>
+        <v>28.84669279388403</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.36773878293183</v>
+        <v>13.59720570381833</v>
       </c>
       <c r="C3" t="n">
-        <v>33.9193831817273</v>
+        <v>32.26022956155019</v>
       </c>
       <c r="D3" t="n">
-        <v>23.16433708170349</v>
+        <v>29.3788000495858</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.86780821729195</v>
+        <v>8.385107141972009</v>
       </c>
       <c r="C4" t="n">
-        <v>49.78737132546849</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D4" t="n">
-        <v>22.93460811890974</v>
+        <v>19.37380919560656</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>13.8063179648229</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43457365470526</v>
+        <v>13.62876431456526</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1086740736188</v>
+        <v>73.75566570235316</v>
       </c>
       <c r="D21" t="n">
-        <v>3.24938392730637</v>
+        <v>1.603384037007678</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.021058670145687</v>
+        <v>2.924626410951248</v>
       </c>
       <c r="C2" t="n">
-        <v>5.957245069369645</v>
+        <v>4.418846416814893</v>
       </c>
       <c r="D2" t="n">
-        <v>16.34708102341364</v>
+        <v>24.14510303824605</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.45609607631404</v>
+        <v>11.04466167277662</v>
       </c>
       <c r="C3" t="n">
-        <v>32.47130531796326</v>
+        <v>31.40610905885546</v>
       </c>
       <c r="D3" t="n">
-        <v>33.24688600431823</v>
+        <v>46.51029748869264</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.78368101436299</v>
+        <v>19.23341927389927</v>
       </c>
       <c r="C4" t="n">
-        <v>70.13114725287089</v>
+        <v>57.82788502324987</v>
       </c>
       <c r="D4" t="n">
-        <v>29.39254451744526</v>
+        <v>30.27317220815464</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.31526418625024</v>
+        <v>8.025787482217677</v>
       </c>
       <c r="C5" t="n">
-        <v>53.8979489631499</v>
+        <v>24.86276061005048</v>
       </c>
       <c r="D5" t="n">
-        <v>31.17048960983623</v>
+        <v>26.89988709636261</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.31700669748049</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.04687151455913</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.39663573917827</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.71871017950435</v>
+        <v>14.83707781903836</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1481965860013</v>
+        <v>87.37390271211476</v>
       </c>
       <c r="D21" t="n">
-        <v>4.179677544876087</v>
+        <v>2.472846303173059</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.462264299980006</v>
+        <v>2.961932823712627</v>
       </c>
       <c r="C2" t="n">
-        <v>10.52237189411731</v>
+        <v>4.141993564217293</v>
       </c>
       <c r="D2" t="n">
-        <v>21.68778853451629</v>
+        <v>31.76051998008856</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.9455872701057</v>
+        <v>10.52924412804704</v>
       </c>
       <c r="C3" t="n">
-        <v>27.13059780686061</v>
+        <v>22.78636421556847</v>
       </c>
       <c r="D3" t="n">
-        <v>38.2734342500619</v>
+        <v>55.03186756155495</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.53966780436203</v>
+        <v>20.49692856926491</v>
       </c>
       <c r="C4" t="n">
-        <v>76.21896476690537</v>
+        <v>70.11838453271569</v>
       </c>
       <c r="D4" t="n">
-        <v>38.90077103307561</v>
+        <v>46.74984392852887</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.23782929080177</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="C5" t="n">
-        <v>93.95325529641977</v>
+        <v>71.56940763959248</v>
       </c>
       <c r="D5" t="n">
-        <v>34.5820628820939</v>
+        <v>31.51410130632262</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.20254312671111</v>
+        <v>7.889324551327369</v>
       </c>
       <c r="C6" t="n">
-        <v>49.30827844579606</v>
+        <v>26.3648345975481</v>
       </c>
       <c r="D6" t="n">
-        <v>37.6755498981756</v>
+        <v>33.6906359666378</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>21.37951975538279</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.82722207071512</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.28806265463436</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03036294970879</v>
+        <v>16.07656394496041</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7680648171617</v>
+        <v>101.536193336592</v>
       </c>
       <c r="D21" t="n">
-        <v>6.010120983236263</v>
+        <v>3.384539777886401</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.52255182056656</v>
+        <v>3.227986451563513</v>
       </c>
       <c r="C2" t="n">
-        <v>8.22115527536279</v>
+        <v>4.972552122010095</v>
       </c>
       <c r="D2" t="n">
-        <v>23.34399691158066</v>
+        <v>37.10809972512094</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.81305133003238</v>
+        <v>10.29362467902781</v>
       </c>
       <c r="C3" t="n">
-        <v>32.5203927031756</v>
+        <v>18.8986433067511</v>
       </c>
       <c r="D3" t="n">
-        <v>42.98582323044659</v>
+        <v>66.9306497370263</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.07798434145878</v>
+        <v>20.3310132072472</v>
       </c>
       <c r="C4" t="n">
-        <v>59.23178424032281</v>
+        <v>62.8053458837812</v>
       </c>
       <c r="D4" t="n">
-        <v>41.63199314629023</v>
+        <v>62.89468492486766</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.6727024660541</v>
+        <v>25.18182861393069</v>
       </c>
       <c r="C5" t="n">
-        <v>88.01368168572657</v>
+        <v>102.8626157124596</v>
       </c>
       <c r="D5" t="n">
-        <v>32.7658296292373</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.49059611468292</v>
+        <v>16.66418553188536</v>
       </c>
       <c r="C6" t="n">
-        <v>67.01900703040852</v>
+        <v>71.48694083243576</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>36.30699359845555</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>29.52409870981433</v>
+        <v>28.20659329071511</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>21.52187317249857</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.03988931668193</v>
+        <v>17.33968410150883</v>
       </c>
       <c r="C21" t="n">
-        <v>65.9989623438931</v>
+        <v>114.4419150699583</v>
       </c>
       <c r="D21" t="n">
-        <v>4.399930822926206</v>
+        <v>4.334921025377207</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.792131528606935</v>
+        <v>2.214822820780804</v>
       </c>
       <c r="C2" t="n">
-        <v>5.541965790473244</v>
+        <v>6.920339567235766</v>
       </c>
       <c r="D2" t="n">
-        <v>20.16902483604647</v>
+        <v>32.53119192792231</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.07031028627405</v>
+        <v>10.67650628368406</v>
       </c>
       <c r="C3" t="n">
-        <v>32.23077713042279</v>
+        <v>19.05081420090935</v>
       </c>
       <c r="D3" t="n">
-        <v>52.20934291184538</v>
+        <v>79.40375431948202</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.46759931132452</v>
+        <v>19.84602984134927</v>
       </c>
       <c r="C4" t="n">
-        <v>72.24975879863551</v>
+        <v>54.67549314491337</v>
       </c>
       <c r="D4" t="n">
-        <v>54.49681506274044</v>
+        <v>80.17540801502001</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.31837366027901</v>
+        <v>27.93072218582176</v>
       </c>
       <c r="C5" t="n">
-        <v>101.0954698448153</v>
+        <v>108.3113154710294</v>
       </c>
       <c r="D5" t="n">
-        <v>40.5216364927871</v>
+        <v>51.86082247683777</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.88181472705867</v>
+        <v>24.63401339496097</v>
       </c>
       <c r="C6" t="n">
-        <v>109.2429940423596</v>
+        <v>116.448040443827</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>40.65417243286043</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.21686843164731</v>
+        <v>13.47448724078747</v>
       </c>
       <c r="C7" t="n">
-        <v>67.97130230352791</v>
+        <v>64.13855926614836</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>30.45872252425729</v>
+        <v>30.95941385342316</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.05772749256809</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.254210613145432</v>
+        <v>17.73349559935125</v>
       </c>
       <c r="C21" t="n">
-        <v>75.26243511138387</v>
+        <v>126.7944935353615</v>
       </c>
       <c r="D21" t="n">
-        <v>5.440657959859074</v>
+        <v>5.320048679805375</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.678248794914303</v>
+        <v>2.116648050356123</v>
       </c>
       <c r="C2" t="n">
-        <v>7.062692984351554</v>
+        <v>4.317726403277472</v>
       </c>
       <c r="D2" t="n">
-        <v>17.74999849278233</v>
+        <v>25.54900225531899</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.41883072128167</v>
+        <v>13.8671863224862</v>
       </c>
       <c r="C3" t="n">
-        <v>25.93777434620073</v>
+        <v>31.4404702285041</v>
       </c>
       <c r="D3" t="n">
-        <v>55.92525797241955</v>
+        <v>87.18901361415924</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.45706212848506</v>
+        <v>13.41361888312417</v>
       </c>
       <c r="C4" t="n">
-        <v>77.06130429714914</v>
+        <v>88.17763355233576</v>
       </c>
       <c r="D4" t="n">
-        <v>67.13190801639689</v>
+        <v>72.5050132017397</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.98858854711009</v>
+        <v>13.8671863224862</v>
       </c>
       <c r="C5" t="n">
-        <v>118.9632780621073</v>
+        <v>69.5813685384927</v>
       </c>
       <c r="D5" t="n">
-        <v>51.00179323562181</v>
+        <v>39.71169463678348</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.15227837181205</v>
+        <v>8.332092765942681</v>
       </c>
       <c r="C6" t="n">
-        <v>135.7285836075301</v>
+        <v>42.22398701195107</v>
       </c>
       <c r="D6" t="n">
-        <v>39.64788103600744</v>
+        <v>25.92206638293279</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.91849924501429</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>116.1201367106085</v>
+        <v>21.73883941513712</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>26.70942804173872</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>61.91882770684633</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
         <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.454093785021173</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>83.85855508148821</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.522332061893526</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
